--- a/docs/audit/SM_Bean_QA_Round1_Retest_Engineering.xlsx
+++ b/docs/audit/SM_Bean_QA_Round1_Retest_Engineering.xlsx
@@ -9146,7 +9146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="30" min="1" max="1"/>
@@ -11997,6 +11997,182 @@
       <c r="R34" s="53" t="inlineStr">
         <is>
           <t>Deploy PR #4; product decision on the self-host page</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="53" t="inlineStr">
+        <is>
+          <t>BUG-34</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>Folder-name migration could abort the deploy or rename another tenant's folder</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="inlineStr">
+        <is>
+          <t>Review of media_library/0004 against 21052a5 data</t>
+        </is>
+      </c>
+      <c r="F35" s="53" t="inlineStr">
+        <is>
+          <t>Migration applies to any real data</t>
+        </is>
+      </c>
+      <c r="G35" s="53" t="inlineStr">
+        <is>
+          <t>IntegrityError 'could not create unique index' on duplicate org-wide subfolders or an existing 'X (2)'; cross-tenant renames</t>
+        </is>
+      </c>
+      <c r="H35" s="53" t="inlineStr">
+        <is>
+          <t>Reproduced on Postgres rewound to 0003</t>
+        </is>
+      </c>
+      <c r="I35" s="53" t="inlineStr">
+        <is>
+          <t>Key includes organisation; de-duplicate every scope with a free suffix</t>
+        </is>
+      </c>
+      <c r="J35" s="53" t="inlineStr">
+        <is>
+          <t>Fixed – retest after deploy</t>
+        </is>
+      </c>
+      <c r="K35" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="53" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+      <c r="M35" s="53" t="inlineStr"/>
+      <c r="N35" s="53" t="inlineStr">
+        <is>
+          <t>Found in pre-deploy migration review (1 Oct)</t>
+        </is>
+      </c>
+      <c r="O35" s="52" t="inlineStr">
+        <is>
+          <t>Fixed in PR #4</t>
+        </is>
+      </c>
+      <c r="P35" s="53" t="inlineStr">
+        <is>
+          <t>Old migration aborts in test; new one passes on every seeded shape</t>
+        </is>
+      </c>
+      <c r="Q35" s="53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R35" s="53" t="inlineStr">
+        <is>
+          <t>Merge PR #4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="53" t="inlineStr">
+        <is>
+          <t>BUG-35</t>
+        </is>
+      </c>
+      <c r="B36" s="53" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" s="53" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="inlineStr">
+        <is>
+          <t>Two workers during a deploy clone the same recurrence dates</t>
+        </is>
+      </c>
+      <c r="E36" s="53" t="inlineStr">
+        <is>
+          <t>Run the recurrence cycle in two workers at once</t>
+        </is>
+      </c>
+      <c r="F36" s="53" t="inlineStr">
+        <is>
+          <t>Each date cloned once</t>
+        </is>
+      </c>
+      <c r="G36" s="53" t="inlineStr">
+        <is>
+          <t>Duplicate scheduled posts (double publish once accounts exist)</t>
+        </is>
+      </c>
+      <c r="H36" s="53" t="inlineStr">
+        <is>
+          <t>Two-thread race test: 24 clones for 12 dates</t>
+        </is>
+      </c>
+      <c r="I36" s="53" t="inlineStr">
+        <is>
+          <t>Re-read the ledger under a row lock per occurrence</t>
+        </is>
+      </c>
+      <c r="J36" s="53" t="inlineStr">
+        <is>
+          <t>Fixed – retest after deploy</t>
+        </is>
+      </c>
+      <c r="K36" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="53" t="inlineStr">
+        <is>
+          <t>Eng</t>
+        </is>
+      </c>
+      <c r="M36" s="53" t="inlineStr"/>
+      <c r="N36" s="53" t="inlineStr">
+        <is>
+          <t>Found in pre-deploy migration review (1 Oct)</t>
+        </is>
+      </c>
+      <c r="O36" s="52" t="inlineStr">
+        <is>
+          <t>Fixed in PR #4</t>
+        </is>
+      </c>
+      <c r="P36" s="53" t="inlineStr">
+        <is>
+          <t>Race test fails without the lock 3/3, passes with it 3/3</t>
+        </is>
+      </c>
+      <c r="Q36" s="53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R36" s="53" t="inlineStr">
+        <is>
+          <t>Merge PR #4</t>
         </is>
       </c>
     </row>

--- a/docs/audit/SM_Bean_QA_Round1_Retest_Engineering.xlsx
+++ b/docs/audit/SM_Bean_QA_Round1_Retest_Engineering.xlsx
@@ -9335,12 +9335,12 @@
       </c>
       <c r="Q2" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: web and worker both on dbe5301 (1 Oct 09:01 UTC)</t>
         </is>
       </c>
       <c r="R2" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="Q3" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Code live; Gmail not connected yet</t>
         </is>
       </c>
       <c r="R3" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4, then connect neopolisinfrallp3@gmail.com at /ops/email/ and send the test email</t>
+          <t>Owner: connect Gmail at /ops/email/, send test email</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="Q4" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: pre-deploy backup db-20261001T090041Z.tar.gz in bucket; legacy media 1 copied, 1 lost (vasavi-atlantis-meta-9x16.mp4 404 on old disk)</t>
         </is>
       </c>
       <c r="R4" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4 (release step also copies existing /media files into the bucket)</t>
+          <t>Re-upload that one video</t>
         </is>
       </c>
     </row>
@@ -9587,12 +9587,12 @@
       </c>
       <c r="Q5" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly: gunicorn logs now level=info JSON; SENTRY_DSN still unset (W005 at boot)</t>
         </is>
       </c>
       <c r="R5" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4; owner: create Sentry project, set SENTRY_DSN on both services</t>
+          <t>Owner: set SENTRY_DSN</t>
         </is>
       </c>
     </row>
@@ -9671,12 +9671,12 @@
       </c>
       <c r="Q6" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: /accounts/signup/ shows 'invite-only' page</t>
         </is>
       </c>
       <c r="R6" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4; owner: set SIGNUP_ALLOWLIST; delete qa-test-noninvited*@example.com; ACCOUNT_EMAIL_VERIFICATION=mandatory after email works</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Q7" s="53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes: worker runs run_worker, 'recurring schedules verified'</t>
         </is>
       </c>
       <c r="R7" s="53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -9839,12 +9839,12 @@
       </c>
       <c r="Q8" s="53" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Partly: admin reachable from any IP (W010 at boot)</t>
         </is>
       </c>
       <c r="R8" s="53" t="inlineStr">
         <is>
-          <t>Owner: delete DJANGO_SUPERUSER_* vars, rotate admin password, set ADMIN_ALLOWED_IPS</t>
+          <t>Owner: ADMIN_ALLOWED_IPS, delete DJANGO_SUPERUSER_*, rotate password</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="Q9" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: /terms/ /privacy/ /support/ 200, own content, no brightbean.xyz</t>
         </is>
       </c>
       <c r="R9" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4; legal review then LEGAL_PAGES_REVIEWED=true</t>
+          <t>Legal review, then LEGAL_PAGES_REVIEWED=true</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="Q11" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: GET /accounts/logout/ returns 405</t>
         </is>
       </c>
       <c r="R11" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="Q12" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R12" s="53" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="Q13" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R13" s="53" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="Q14" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R14" s="53" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="Q15" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R15" s="53" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="Q16" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R16" s="53" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="Q17" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R17" s="53" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="Q18" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R18" s="53" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="Q19" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R19" s="53" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="Q20" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R20" s="53" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="Q21" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R21" s="53" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="Q22" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R22" s="53" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="Q23" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R23" s="53" t="inlineStr">
@@ -11179,12 +11179,12 @@
       </c>
       <c r="Q24" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes on login, signup, marketing; marketing 'Source code' links still went to upstream repo: fixed in PR #5</t>
         </is>
       </c>
       <c r="R24" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4</t>
+          <t>Merge PR #5</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11263,12 @@
       </c>
       <c r="Q25" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: branded 404; invalid portal link shows 'This link isn't valid'</t>
         </is>
       </c>
       <c r="R25" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="Q26" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: robots.txt + sitemap, page titles on every public page</t>
         </is>
       </c>
       <c r="R26" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="Q28" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R28" s="53" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="Q29" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R29" s="53" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="Q30" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R30" s="53" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="Q31" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes (dbe5301, 1 Oct). Behind login: needs QA retest signed in</t>
         </is>
       </c>
       <c r="R31" s="53" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="Q32" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: gunicorn booted, /health/ 200 with database+cache checks</t>
         </is>
       </c>
       <c r="R32" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -11911,12 +11911,12 @@
       </c>
       <c r="Q33" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: release ran backup then 8 migrations then media import; worker errors stopped</t>
         </is>
       </c>
       <c r="R33" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4 (worker errors stop once migrate runs)</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -11991,12 +11991,12 @@
       </c>
       <c r="Q34" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes except 'Source code' links → upstream repo; fixed in PR #5</t>
         </is>
       </c>
       <c r="R34" s="53" t="inlineStr">
         <is>
-          <t>Deploy PR #4; product decision on the self-host page</t>
+          <t>Merge PR #5; product decision on self-host page</t>
         </is>
       </c>
     </row>
@@ -12079,12 +12079,12 @@
       </c>
       <c r="Q35" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: media_library.0004 applied OK on production data</t>
         </is>
       </c>
       <c r="R35" s="53" t="inlineStr">
         <is>
-          <t>Merge PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -12167,12 +12167,12 @@
       </c>
       <c r="Q36" s="53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes: worker live; first cycle 'Generated 0 recurring posts' (no surprise clones)</t>
         </is>
       </c>
       <c r="R36" s="53" t="inlineStr">
         <is>
-          <t>Merge PR #4</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
